--- a/testakten/scheidungsdrama/xlsx/unterhaltsberechnung_kindesunterhalt_trennungsunterhalt.xlsx
+++ b/testakten/scheidungsdrama/xlsx/unterhaltsberechnung_kindesunterhalt_trennungsunterhalt.xlsx
@@ -648,7 +648,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Kindesunterhalt — Wagenknecht (Theo barunterhaltspflichtig)</t>
+          <t>Kindesunterhalt — Trüffelberch (Franz barunterhaltspflichtig)</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
     </row>
     <row r="10">
       <c r="B10" s="10">
-        <f> Bereinigtes Nettoeinkommen Theo (vorläufig)</f>
+        <f> Bereinigtes Nettoeinkommen Franz (vorläufig)</f>
         <v/>
       </c>
       <c r="F10" s="11" t="n">
@@ -739,7 +739,7 @@
     <row r="14">
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Bereinigtes Nettoeinkommen Theo</t>
+          <t>Bereinigtes Nettoeinkommen Franz</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
@@ -1017,7 +1017,7 @@
     <row r="34" ht="36" customHeight="1">
       <c r="B34" s="31" t="inlineStr">
         <is>
-          <t>⚠ Mangelfall-Berechnung gilt, wenn Theos tatsächliches Einkommen ≤ 2.813 EUR. Jahresabschlüsse Theo noch unvollständig. Bei höherem Einkommen entfällt der Mangelfall.</t>
+          <t>⚠ Mangelfall-Berechnung gilt, wenn Franz' tatsächliches Einkommen ≤ 2.813 EUR. Jahresabschlüsse Franz noch unvollständig. Bei höherem Einkommen entfällt der Mangelfall.</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Trennungsunterhalt — § 1361 BGB — Theo gegen Vera (vorläufige Berechnung)</t>
+          <t>Trennungsunterhalt — § 1361 BGB — Franz gegen Hanna (vorläufige Berechnung)</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Vera (EUR/Monat)</t>
+          <t>Hanna (EUR/Monat)</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Theo (EUR/Monat)</t>
+          <t>Franz (EUR/Monat)</t>
         </is>
       </c>
       <c r="E4" s="12" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Vera: Inhaberentnahme + Gehalt; Theo: bereinigt</t>
+          <t>Hanna: Inhaberentnahme + Gehalt; Franz: bereinigt</t>
         </is>
       </c>
     </row>
@@ -1121,14 +1121,14 @@
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Vera − Theo</t>
+          <t>Hanna − Franz</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>3/7 der Differenz = Bedarf Theo</t>
+          <t>3/7 der Differenz = Bedarf Franz</t>
         </is>
       </c>
       <c r="C7" s="33" t="inlineStr"/>
@@ -1144,7 +1144,7 @@
     <row r="8">
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Abzug: eigenes Einkommen Theo</t>
+          <t>Abzug: eigenes Einkommen Franz</t>
         </is>
       </c>
       <c r="C8" s="32" t="inlineStr"/>
@@ -1160,7 +1160,7 @@
     <row r="9">
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Vorwegabzug Kindesunterhalt (Theo zahlt)</t>
+          <t>Vorwegabzug Kindesunterhalt (Franz zahlt)</t>
         </is>
       </c>
       <c r="C9" s="33" t="inlineStr"/>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="10">
       <c r="B10" s="34">
-        <f> Verfügbar Theo nach Kindesunterhalt</f>
+        <f> Verfügbar Franz nach Kindesunterhalt</f>
         <v/>
       </c>
       <c r="C10" s="35" t="inlineStr"/>
